--- a/data/trans_dic/P21B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,11; 100,0</t>
+          <t>94,31; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,76; 99,26</t>
+          <t>91,13; 99,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94,29; 100,0</t>
+          <t>93,7; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,78; 97,52</t>
+          <t>80,18; 97,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,83; 100,0</t>
+          <t>96,81; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,47; 99,51</t>
+          <t>96,07; 99,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,65; 97,81</t>
+          <t>89,18; 97,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,72; 97,66</t>
+          <t>92,09; 97,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>97,13; 99,66</t>
+          <t>96,79; 99,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94,94; 99,1</t>
+          <t>95,04; 99,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93,46; 98,3</t>
+          <t>93,04; 98,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,46; 96,68</t>
+          <t>88,92; 96,78</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,25; 99,43</t>
+          <t>95,33; 99,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,65; 99,53</t>
+          <t>94,97; 99,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,47; 94,33</t>
+          <t>83,53; 94,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,76; 96,89</t>
+          <t>90,51; 96,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,2; 99,04</t>
+          <t>95,01; 99,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,2; 100,0</t>
+          <t>97,96; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,43; 97,74</t>
+          <t>91,16; 97,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>91,17; 96,51</t>
+          <t>91,0; 96,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96,12; 99,0</t>
+          <t>96,1; 98,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97,75; 99,61</t>
+          <t>97,73; 99,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,55; 95,26</t>
+          <t>89,16; 95,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,68; 96,22</t>
+          <t>92,2; 96,18</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,23; 95,59</t>
+          <t>84,42; 95,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>93,49; 98,91</t>
+          <t>93,15; 98,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,14; 97,62</t>
+          <t>88,88; 97,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,8; 95,37</t>
+          <t>83,87; 94,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,31; 97,53</t>
+          <t>89,96; 97,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,41; 98,33</t>
+          <t>92,28; 98,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,41; 95,0</t>
+          <t>85,71; 95,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,1; 98,75</t>
+          <t>83,86; 92,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,92; 95,88</t>
+          <t>89,25; 96,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93,65; 97,96</t>
+          <t>94,0; 97,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,26; 95,72</t>
+          <t>88,87; 95,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,33; 98,0</t>
+          <t>85,65; 92,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,32; 96,51</t>
+          <t>88,25; 96,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95,02; 99,41</t>
+          <t>95,01; 99,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,13; 94,89</t>
+          <t>85,2; 94,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81,28; 91,3</t>
+          <t>81,85; 91,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,18; 97,86</t>
+          <t>92,2; 97,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,65; 95,67</t>
+          <t>88,16; 95,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,13; 93,55</t>
+          <t>85,2; 93,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,75; 92,24</t>
+          <t>85,98; 92,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,05; 96,64</t>
+          <t>92,02; 96,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92,08; 96,98</t>
+          <t>92,2; 96,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87,03; 93,16</t>
+          <t>86,86; 93,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,04; 90,85</t>
+          <t>85,88; 91,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,91</t>
+          <t>93,1; 96,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,88; 98,46</t>
+          <t>95,99; 98,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,58</t>
+          <t>90,25; 94,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,66; 93,49</t>
+          <t>88,48; 93,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>95,29; 97,81</t>
+          <t>95,36; 97,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,58; 97,89</t>
+          <t>95,44; 97,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,33; 94,61</t>
+          <t>90,08; 94,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,89; 96,5</t>
+          <t>89,83; 93,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,04; 97,16</t>
+          <t>95,08; 97,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96,08; 97,81</t>
+          <t>96,06; 97,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91,07; 94,09</t>
+          <t>91,18; 94,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,08</t>
+          <t>89,96; 92,83</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120283</t>
+          <t>129277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>136458</t>
+          <t>146763</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>256741</t>
+          <t>276040</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>107264; 112781</t>
+          <t>106359; 112781</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>128355; 140373</t>
+          <t>128879; 140378</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96136; 101961</t>
+          <t>95537; 101961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106481; 125445</t>
+          <t>111068; 134751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131778; 136096</t>
+          <t>131752; 136096</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>184621; 192449</t>
+          <t>185796; 192452</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>123902; 135181</t>
+          <t>123252; 134851</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131245; 139752</t>
+          <t>141523; 149804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>241747; 248038</t>
+          <t>240881; 248025</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>317879; 331792</t>
+          <t>318214; 331721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224452; 236080</t>
+          <t>223447; 235866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>243072; 262715</t>
+          <t>259835; 282817</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201275</t>
+          <t>221130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>222788</t>
+          <t>246048</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>424064</t>
+          <t>467178</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176794; 184566</t>
+          <t>176940; 184571</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>218957; 227830</t>
+          <t>217393; 227664</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144936; 161858</t>
+          <t>143328; 161641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>191811; 207040</t>
+          <t>212125; 227060</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>270314; 281204</t>
+          <t>269770; 281156</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>293934; 299316</t>
+          <t>293212; 299316</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>193722; 207087</t>
+          <t>193143; 206599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>215289; 227901</t>
+          <t>237242; 251641</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>451335; 464838</t>
+          <t>451247; 464332</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516315; 526173</t>
+          <t>516217; 526124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>343390; 365296</t>
+          <t>341914; 365283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>412408; 432820</t>
+          <t>456435; 476158</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127680</t>
+          <t>137943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>368818</t>
+          <t>193095</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>496498</t>
+          <t>331038</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>104149; 118199</t>
+          <t>104384; 118205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>169982; 179848</t>
+          <t>169372; 179014</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112483; 123183</t>
+          <t>112160; 123222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119751; 133107</t>
+          <t>128146; 144642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>159439; 172182</t>
+          <t>158808; 172042</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>238443; 253713</t>
+          <t>238104; 253820</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>130913; 145628</t>
+          <t>131376; 146103</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>339485; 384905</t>
+          <t>182801; 201401</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>266926; 287838</t>
+          <t>267923; 288244</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>411927; 430885</t>
+          <t>413454; 430777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>249469; 267525</t>
+          <t>248374; 266627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>467586; 518769</t>
+          <t>317579; 341721</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>168674</t>
+          <t>180586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>248061</t>
+          <t>271198</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>416736</t>
+          <t>451784</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120457; 131633</t>
+          <t>120361; 131654</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143909; 150555</t>
+          <t>143889; 150557</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130684; 143972</t>
+          <t>129274; 144070</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157958; 177430</t>
+          <t>169234; 189841</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>209659; 222564</t>
+          <t>209706; 222711</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198639; 216814</t>
+          <t>199801; 216927</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>209367; 230073</t>
+          <t>209541; 230279</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>237945; 255967</t>
+          <t>259982; 279825</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>334922; 351609</t>
+          <t>334820; 352174</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>348133; 366673</t>
+          <t>348604; 366302</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>346069; 370457</t>
+          <t>345393; 370383</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>401243; 428662</t>
+          <t>437246; 464551</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>617913</t>
+          <t>668936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>976126</t>
+          <t>857103</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1594039</t>
+          <t>1526040</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>521171; 541164</t>
+          <t>519926; 541582</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>674598; 692771</t>
+          <t>675363; 693539</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>496819; 521563</t>
+          <t>497676; 522076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>599556; 632172</t>
+          <t>648060; 683339</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>785172; 805944</t>
+          <t>785811; 805989</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>934131; 956720</t>
+          <t>932772; 956899</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>676864; 708890</t>
+          <t>674988; 708250</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>951186; 1009867</t>
+          <t>839627; 871099</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1313868; 1343182</t>
+          <t>1314420; 1343697</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1615024; 1644064</t>
+          <t>1614688; 1644620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1184632; 1223872</t>
+          <t>1186026; 1225070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1566789; 1637961</t>
+          <t>1499867; 1547622</t>
         </is>
       </c>
     </row>
